--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>88728</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>88728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>88729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>88728</v>
+        <v>75138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91339</v>
+        <v>91340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91697</v>
+        <v>91698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>97469</v>
+        <v>97470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>127311786</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91685</v>
+        <v>91686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B13" t="n">
-        <v>91322</v>
+        <v>80118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B14" t="n">
-        <v>80118</v>
+        <v>91322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309455</v>
+        <v>127309355</v>
       </c>
       <c r="B3" t="n">
-        <v>88729</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447068</v>
+        <v>447105</v>
       </c>
       <c r="R3" t="n">
-        <v>7088551</v>
+        <v>7088514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309355</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447105</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088514</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>88729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>88729</v>
+        <v>97470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R11" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>97470</v>
+        <v>88729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R12" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127309509</v>
       </c>
       <c r="B2" t="n">
-        <v>77997</v>
+        <v>78001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>88733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>88729</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91698</v>
+        <v>91702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>97470</v>
+        <v>97474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>80118</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R13" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91322</v>
+        <v>80122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
         <v>127311786</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>127311278</v>
       </c>
       <c r="B16" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127311468</v>
       </c>
       <c r="B17" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R18" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B19" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R19" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91686</v>
+        <v>91690</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309455</v>
+        <v>127309355</v>
       </c>
       <c r="B3" t="n">
-        <v>88733</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447068</v>
+        <v>447105</v>
       </c>
       <c r="R3" t="n">
-        <v>7088551</v>
+        <v>7088514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309355</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447105</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088514</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>88733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>97474</v>
+        <v>88733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R11" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>88733</v>
+        <v>97474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R12" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127311786</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>91784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446306</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127311786</v>
+        <v>127310600</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446306</v>
+        <v>446304</v>
       </c>
       <c r="R15" t="n">
-        <v>7088345</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>88733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>88733</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1792,45 +1792,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127311786</v>
+        <v>127312076</v>
       </c>
       <c r="B13" t="n">
-        <v>91784</v>
+        <v>80122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446306</v>
+        <v>446683</v>
       </c>
       <c r="R13" t="n">
-        <v>7088345</v>
+        <v>7088160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B14" t="n">
-        <v>80122</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127310600</v>
+        <v>127311786</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446304</v>
+        <v>446306</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R18" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R19" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1792,45 +1792,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B13" t="n">
-        <v>80122</v>
+        <v>91784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R13" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>80122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127311786</v>
+        <v>127310600</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446306</v>
+        <v>446304</v>
       </c>
       <c r="R15" t="n">
-        <v>7088345</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1792,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127311786</v>
+        <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>91784</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446306</v>
+        <v>446304</v>
       </c>
       <c r="R13" t="n">
-        <v>7088345</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B14" t="n">
-        <v>80122</v>
+        <v>91784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>80122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R18" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R19" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>88733</v>
+        <v>97474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R11" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>97474</v>
+        <v>88733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R12" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R18" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R19" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127309509</v>
       </c>
       <c r="B2" t="n">
-        <v>78001</v>
+        <v>78003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309455</v>
+        <v>127309355</v>
       </c>
       <c r="B3" t="n">
-        <v>88733</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447068</v>
+        <v>447105</v>
       </c>
       <c r="R3" t="n">
-        <v>7088551</v>
+        <v>7088514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309355</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>75144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447105</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088514</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>88735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91702</v>
+        <v>91704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>97474</v>
+        <v>88735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R11" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>88733</v>
+        <v>97476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R12" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
         <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127311786</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91784</v>
+        <v>80124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446306</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088345</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,45 +1996,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B15" t="n">
-        <v>80122</v>
+        <v>91786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R15" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
         <v>127311278</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127311468</v>
       </c>
       <c r="B17" t="n">
-        <v>75147</v>
+        <v>75149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>88735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>88735</v>
+        <v>75144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B13" t="n">
-        <v>91328</v>
+        <v>80124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B14" t="n">
-        <v>80124</v>
+        <v>91328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R18" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R19" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>88735</v>
+        <v>97476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R11" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>97476</v>
+        <v>88735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R12" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>97476</v>
+        <v>88735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R11" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>88735</v>
+        <v>97476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R12" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>80124</v>
+        <v>91328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R13" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91328</v>
+        <v>80124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R18" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R19" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309455</v>
+        <v>127309355</v>
       </c>
       <c r="B3" t="n">
-        <v>88735</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447068</v>
+        <v>447105</v>
       </c>
       <c r="R3" t="n">
-        <v>7088551</v>
+        <v>7088514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309355</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447105</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088514</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>75144</v>
+        <v>88741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91704</v>
+        <v>91710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>97476</v>
+        <v>97482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B13" t="n">
-        <v>91328</v>
+        <v>80124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B14" t="n">
-        <v>80124</v>
+        <v>91792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127311786</v>
+        <v>127310600</v>
       </c>
       <c r="B15" t="n">
-        <v>91786</v>
+        <v>91334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446306</v>
+        <v>446304</v>
       </c>
       <c r="R15" t="n">
-        <v>7088345</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>91698</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127309509</v>
       </c>
       <c r="B2" t="n">
-        <v>78003</v>
+        <v>78006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309405</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>75147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447088</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309455</v>
       </c>
       <c r="B4" t="n">
-        <v>75144</v>
+        <v>88744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447068</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,7 +963,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -976,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309355</v>
       </c>
       <c r="B5" t="n">
-        <v>88741</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447105</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91710</v>
+        <v>91713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>97482</v>
+        <v>97485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>80124</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R13" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
         <v>127311786</v>
       </c>
       <c r="B14" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B15" t="n">
-        <v>91334</v>
+        <v>80127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
         <v>127311278</v>
       </c>
       <c r="B16" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127311468</v>
       </c>
       <c r="B17" t="n">
-        <v>75149</v>
+        <v>75152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127309509</v>
       </c>
       <c r="B2" t="n">
-        <v>78006</v>
+        <v>78012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B3" t="n">
-        <v>75147</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R3" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B4" t="n">
-        <v>88744</v>
+        <v>75153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R4" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +958,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>88752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R5" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91713</v>
+        <v>91721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>97485</v>
+        <v>97493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127311786</v>
       </c>
       <c r="B13" t="n">
-        <v>91337</v>
+        <v>91803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446306</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127311786</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>80133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446306</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088345</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127312076</v>
+        <v>127310600</v>
       </c>
       <c r="B15" t="n">
-        <v>80127</v>
+        <v>91345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446683</v>
+        <v>446304</v>
       </c>
       <c r="R15" t="n">
-        <v>7088160</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
         <v>127311278</v>
       </c>
       <c r="B16" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>127311468</v>
       </c>
       <c r="B17" t="n">
-        <v>75152</v>
+        <v>75158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91701</v>
+        <v>91709</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309355</v>
+        <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>88753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447105</v>
+        <v>447068</v>
       </c>
       <c r="R3" t="n">
-        <v>7088514</v>
+        <v>7088551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bördig och örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127309405</v>
+        <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447088</v>
+        <v>447105</v>
       </c>
       <c r="R4" t="n">
-        <v>7088530</v>
+        <v>7088514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127309455</v>
+        <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>88752</v>
+        <v>75153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447068</v>
+        <v>447088</v>
       </c>
       <c r="R5" t="n">
-        <v>7088551</v>
+        <v>7088530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127311314</v>
       </c>
       <c r="B11" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127310511</v>
       </c>
       <c r="B12" t="n">
-        <v>97493</v>
+        <v>97494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127311786</v>
+        <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>91803</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446306</v>
+        <v>446304</v>
       </c>
       <c r="R13" t="n">
-        <v>7088345</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B14" t="n">
-        <v>80133</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127310600</v>
+        <v>127312076</v>
       </c>
       <c r="B15" t="n">
-        <v>91345</v>
+        <v>80133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,34 +2007,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446304</v>
+        <v>446683</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B18" t="n">
-        <v>91349</v>
+        <v>91368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R18" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B19" t="n">
-        <v>91367</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R19" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127311314</v>
+        <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>88753</v>
+        <v>97494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>222741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445889</v>
+        <v>446354</v>
       </c>
       <c r="R11" t="n">
-        <v>7088575</v>
+        <v>7088716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127310511</v>
+        <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>97494</v>
+        <v>88753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222741</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446354</v>
+        <v>445889</v>
       </c>
       <c r="R12" t="n">
-        <v>7088716</v>
+        <v>7088575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310074</v>
+        <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446430</v>
+        <v>446411</v>
       </c>
       <c r="R18" t="n">
-        <v>7088536</v>
+        <v>7088540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310147</v>
+        <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>91368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446411</v>
+        <v>446430</v>
       </c>
       <c r="R19" t="n">
-        <v>7088540</v>
+        <v>7088536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127309455</v>
       </c>
       <c r="B3" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127309546</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127309851</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127310736</v>
       </c>
       <c r="B8" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127310231</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127310064</v>
       </c>
       <c r="B10" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>127310511</v>
       </c>
       <c r="B11" t="n">
-        <v>97494</v>
+        <v>97495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127311314</v>
       </c>
       <c r="B12" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>127310600</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,45 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127311786</v>
+        <v>127312076</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>80133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446306</v>
+        <v>446683</v>
       </c>
       <c r="R14" t="n">
-        <v>7088345</v>
+        <v>7088160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,45 +1996,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127312076</v>
+        <v>127311786</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>91805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446683</v>
+        <v>446306</v>
       </c>
       <c r="R15" t="n">
-        <v>7088160</v>
+        <v>7088345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
         <v>127310147</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>127310074</v>
       </c>
       <c r="B19" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127310078</v>
       </c>
       <c r="B20" t="n">
-        <v>91710</v>
+        <v>91711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>127311788</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>127311802</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127309509</v>
+        <v>127309455</v>
       </c>
       <c r="B2" t="n">
-        <v>78012</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447060</v>
+        <v>447068</v>
       </c>
       <c r="R2" t="n">
-        <v>7088554</v>
+        <v>7088551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127309455</v>
+        <v>127309312</v>
       </c>
       <c r="B3" t="n">
-        <v>88754</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447068</v>
+        <v>447169</v>
       </c>
       <c r="R3" t="n">
-        <v>7088551</v>
+        <v>7088496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -882,11 +877,11 @@
         <v>127309355</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -979,7 +974,7 @@
         <v>127309405</v>
       </c>
       <c r="B5" t="n">
-        <v>75153</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127309546</v>
+        <v>127309509</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>78339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446978</v>
+        <v>447060</v>
       </c>
       <c r="R6" t="n">
-        <v>7088562</v>
+        <v>7088554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127309851</v>
+        <v>127311314</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446491</v>
+        <v>445889</v>
       </c>
       <c r="R7" t="n">
-        <v>7088600</v>
+        <v>7088575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127310736</v>
+        <v>127310600</v>
       </c>
       <c r="B8" t="n">
-        <v>91365</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446210</v>
+        <v>446304</v>
       </c>
       <c r="R8" t="n">
-        <v>7088749</v>
+        <v>7088753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127310231</v>
+        <v>127310147</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446384</v>
+        <v>446411</v>
       </c>
       <c r="R9" t="n">
-        <v>7088629</v>
+        <v>7088540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127310064</v>
+        <v>127310231</v>
       </c>
       <c r="B10" t="n">
-        <v>91723</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1505</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446430</v>
+        <v>446384</v>
       </c>
       <c r="R10" t="n">
-        <v>7088536</v>
+        <v>7088629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127310511</v>
+        <v>127311788</v>
       </c>
       <c r="B11" t="n">
-        <v>97495</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446354</v>
+        <v>446306</v>
       </c>
       <c r="R11" t="n">
-        <v>7088716</v>
+        <v>7088345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1685,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127311314</v>
+        <v>127310736</v>
       </c>
       <c r="B12" t="n">
-        <v>88754</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445889</v>
+        <v>446210</v>
       </c>
       <c r="R12" t="n">
-        <v>7088575</v>
+        <v>7088749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127310600</v>
+        <v>127311786</v>
       </c>
       <c r="B13" t="n">
-        <v>91347</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446304</v>
+        <v>446306</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127312076</v>
+        <v>127311468</v>
       </c>
       <c r="B14" t="n">
-        <v>80133</v>
+        <v>83312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1900,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446683</v>
+        <v>445915</v>
       </c>
       <c r="R14" t="n">
-        <v>7088160</v>
+        <v>7088457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,7 +1973,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Bördig och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1996,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127311786</v>
+        <v>127310064</v>
       </c>
       <c r="B15" t="n">
-        <v>91805</v>
+        <v>92295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1505</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446306</v>
+        <v>446430</v>
       </c>
       <c r="R15" t="n">
-        <v>7088345</v>
+        <v>7088536</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,45 +2093,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127311278</v>
+        <v>127310078</v>
       </c>
       <c r="B16" t="n">
-        <v>80133</v>
+        <v>92283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästgätarflon, Hästgätarflon, Jmt</t>
+          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445895</v>
+        <v>446430</v>
       </c>
       <c r="R16" t="n">
-        <v>7088596</v>
+        <v>7088536</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127311468</v>
+        <v>127311278</v>
       </c>
       <c r="B17" t="n">
-        <v>75158</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2206,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445915</v>
+        <v>445895</v>
       </c>
       <c r="R17" t="n">
-        <v>7088457</v>
+        <v>7088596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127310147</v>
+        <v>127312076</v>
       </c>
       <c r="B18" t="n">
-        <v>91351</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2313,34 +2308,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
+          <t>Ansättån, Ansättån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446411</v>
+        <v>446683</v>
       </c>
       <c r="R18" t="n">
-        <v>7088540</v>
+        <v>7088160</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,7 +2381,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Bördig och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2404,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127310074</v>
+        <v>127310511</v>
       </c>
       <c r="B19" t="n">
-        <v>91369</v>
+        <v>98137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>222741</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446430</v>
+        <v>446354</v>
       </c>
       <c r="R19" t="n">
-        <v>7088536</v>
+        <v>7088716</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,312 +2498,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>127310078</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91711</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2063</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Grantickeporing</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>446430</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7088536</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>127311788</v>
-      </c>
-      <c r="B21" t="n">
-        <v>91351</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>446306</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7088345</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>127311802</v>
-      </c>
-      <c r="B22" t="n">
-        <v>91369</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Svartrutjärnen, Svartrutjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>446325</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7088313</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60873-2024 artfynd.xlsx
+++ b/artfynd/A 60873-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127309455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127309312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127309355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127309405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127309509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311314</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310147</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310231</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311788</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310736</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311786</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311468</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310064</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310078</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311278</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127312076</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,8 +2588,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127310511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>